--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -808,7 +808,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£14.17</t>
+          <t>£14.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -928,7 +928,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.73</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£20.58</t>
+          <t>£20.53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£25.38</t>
+          <t>£25.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>£46.74</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£37.25</t>
+          <t>£38.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£37.73</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£27.69</t>
+          <t>£27.00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£33.36</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£36.25</t>
+          <t>£36.00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£41.34</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6dcb3a235
-	0x7ff6dc892650
-	0x7ff6dc6216dd
-	0x7ff6dc67a27e
-	0x7ff6dc67a58c
-	0x7ff6dc6ced77
-	0x7ff6dc6cbaba
-	0x7ff6dc66b0ed
-	0x7ff6dc66bf63
-	0x7ff6dcb65d60
-	0x7ff6dcb5fe8a
-	0x7ff6dcb81005
-	0x7ff6dc8ad73e
-	0x7ff6dc8b4e3f
-	0x7ff6dc89b7e4
-	0x7ff6dc89b99f
-	0x7ff6dc881908
+	0x7ff7c8b6a235
+	0x7ff7c88c2650
+	0x7ff7c86516dd
+	0x7ff7c86aa27e
+	0x7ff7c86aa58c
+	0x7ff7c86fed77
+	0x7ff7c86fbaba
+	0x7ff7c869b0ed
+	0x7ff7c869bf63
+	0x7ff7c8b95d60
+	0x7ff7c8b8fe8a
+	0x7ff7c8bb1005
+	0x7ff7c88dd73e
+	0x7ff7c88e4e3f
+	0x7ff7c88cb7e4
+	0x7ff7c88cb99f
+	0x7ff7c88b1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>£67.41</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/5-boards-x-115mm-celotex-thermaclass-cavity-wall-21-insulation</t>
+          <t>£1248.32</t>
         </is>
       </c>
     </row>
